--- a/GameData/DataTables/Meta/MaterialTable.xlsx
+++ b/GameData/DataTables/Meta/MaterialTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MaterialKind</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>StackLimit</t>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>IsTypedByCase</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FlavorText</t>
         </is>
       </c>
     </row>
@@ -477,12 +487,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>int</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -494,22 +514,188 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>材料的基础定义</t>
+          <t>材料的完整静态定义</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>稳定键（MT-001~MT-006）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>材料显示名称</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>材料大类（占位，取值域待 P0-011 冻结）</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>单格堆叠上限，0 表示不限</t>
+          <t>材料稀有度（Common=0、Refined=1、Rare=2）</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>是否按来源怪谈类型化</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>材料风味描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MT-001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>铜芯线</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>细细的铜线绕成一圈，像把没说完的话收进了口袋。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MT-002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>精密齿轮</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>每一枚齿都认真咬合，只有时间偶尔偷懒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MT-003</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>玻璃镜片</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>擦净之后，映出来的世界似乎比昨天清楚一点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MT-004</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>校准簧片</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>轻轻一拨就会颤动，像在替某台旧机器清嗓子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MT-005</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>定势残晶</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>一小块安静的光，握久了，总觉得它记得某个瞬间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MT-006</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>异常纹样</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>纹路没有固定的方向。你移开视线时，它似乎又换了一种写法。</t>
         </is>
       </c>
     </row>
